--- a/resources/templates/import/template-input-rekanan.xlsx
+++ b/resources/templates/import/template-input-rekanan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\project-ABAH\resources\templates\import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1C62E2-8C63-4A67-AAA7-6023E8B3CE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805C55D4-01FB-4E00-B9CC-C9A8C202D0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,15 +63,21 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -79,13 +85,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -390,13 +415,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.36328125" customWidth="1"/>
     <col min="2" max="3" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
     <col min="6" max="8" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -426,8 +451,108 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:H1" xr:uid="{79E9CF25-73DA-4877-83DB-0DDFC8C75A9E}">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
@@ -438,15 +563,13 @@
         </mc:Fallback>
       </mc:AlternateContent>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A60" xr:uid="{2F614A86-B250-4D29-9F5D-6B1045C6F3C1}">
-      <formula1>"BRI Life, BRI Finance, BRI Danareksa Sekuritas, BRINS, Pegadaian, PNM"</formula1>
-    </dataValidation>
-    <dataValidation showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="B1" xr:uid="{1981D10C-7C14-4353-B9C2-511769CE1988}"/>
-    <dataValidation showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="F1 E1 C1" xr:uid="{5A7C195E-8541-4291-9DC5-E2867796A96E}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D60" xr:uid="{B059B4B0-87CD-41EF-BC53-D10E39A82DE2}">
+    <dataValidation showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="E1:F1 C1" xr:uid="{1981D10C-7C14-4353-B9C2-511769CE1988}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{B059B4B0-87CD-41EF-BC53-D10E39A82DE2}">
       <formula1>"Sudah Nasabah, Belum Nasabah"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Mohon maaf, silakan pilih status yang tersedia di daftar" sqref="A1" xr:uid="{ACCD9EA5-79D9-42A2-BE51-C78683A4CD00}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{0D71F64A-F761-4D40-A308-0DE6093BD341}">
+      <formula1>"BRI Life, BRI Finance, BRI Danareksa Sekuritas, BRI Insurance (BRINS), Pegadaian, PNM (Permodalan Nasional Madani)"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
